--- a/ISRPO_dolgs.xlsx
+++ b/ISRPO_dolgs.xlsx
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -138,10 +138,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -468,21 +471,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
       <c r="Q1" t="s">
         <v>5</v>
       </c>
@@ -491,19 +494,19 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
       <c r="Q2" t="s">
         <v>4</v>
       </c>
@@ -512,25 +515,25 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="Q3" t="s">
@@ -541,7 +544,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -572,8 +575,8 @@
       <c r="K4" s="2">
         <v>10</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -684,7 +687,7 @@
         <v>6</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -729,17 +732,17 @@
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>4</v>
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>4</v>
@@ -766,11 +769,11 @@
       <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -804,10 +807,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -840,23 +843,23 @@
       <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>4</v>
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>4</v>
@@ -915,19 +918,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>4</v>
@@ -1165,21 +1168,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
       <c r="Q1" t="s">
         <v>5</v>
       </c>
@@ -1188,19 +1191,19 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
       <c r="Q2" t="s">
         <v>4</v>
       </c>
@@ -1209,25 +1212,25 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="Q3" t="s">
@@ -1238,7 +1241,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1269,8 +1272,8 @@
       <c r="K4" s="2">
         <v>10</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
